--- a/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/Risk_Velocity_FINAL_QUALITATIVE_ANALYSIS_20260828_133159.xlsx
+++ b/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/Risk_Velocity_FINAL_QUALITATIVE_ANALYSIS_20260828_133159.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_BFAC15303878AF7A201278AAEA7E660A8F8D4B87" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97DABFD6-BBAF-44CD-ABA4-B8EC31FA0E23}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_RV_Evidence" sheetId="1" r:id="rId1"/>
@@ -485,6 +485,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
